--- a/output/pdf_financials_xlsx/BKM.xlsx
+++ b/output/pdf_financials_xlsx/BKM.xlsx
@@ -7211,61 +7211,61 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>0.099117</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>0.007129</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.004547</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>-0.008035</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>0.001089</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>-0.010839</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>0.009664000000000001</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>-0.000163</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>-0.010581</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>0.002869</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0</v>
+        <v>-0.030244</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>0</v>
+        <v>0.004459</v>
       </c>
       <c r="N103" s="3" t="n">
-        <v>0</v>
+        <v>-0.010646</v>
       </c>
       <c r="O103" s="3" t="n">
-        <v>0</v>
+        <v>0.0007560000000000001</v>
       </c>
       <c r="P103" s="3" t="n">
-        <v>0</v>
+        <v>0.07055400000000001</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>0</v>
+        <v>0.001132</v>
       </c>
       <c r="R103" s="3" t="n">
-        <v>0</v>
+        <v>0.001294</v>
       </c>
       <c r="S103" s="3" t="n">
-        <v>0</v>
+        <v>-0.020313</v>
       </c>
       <c r="T103" s="3" t="n">
-        <v>0</v>
+        <v>-0.001202</v>
       </c>
     </row>
     <row r="104">
@@ -7403,61 +7403,61 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.009801000000000001</v>
+        <v>0.108918</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.042825</v>
+        <v>0.049954</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.0369</v>
+        <v>-0.041447</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.011668</v>
+        <v>0.003633</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.008248</v>
+        <v>-0.007159</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.025444</v>
+        <v>-0.036283</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-0.013642</v>
+        <v>-0.003978</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.002502</v>
+        <v>0.002339</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>-0.019767</v>
+        <v>-0.030348</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.008069</v>
+        <v>0.010938</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>-0.009287</v>
+        <v>-0.039531</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0.002235</v>
+        <v>0.006694</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>-0.001724</v>
+        <v>-0.01237</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0.002663</v>
+        <v>0.003419</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>0.013037</v>
+        <v>0.083591</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>-0.0025</v>
+        <v>-0.001368</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>-0.007827000000000001</v>
+        <v>-0.006533</v>
       </c>
       <c r="S106" s="3" t="n">
-        <v>0.017756</v>
+        <v>-0.002557</v>
       </c>
       <c r="T106" s="3" t="n">
-        <v>-0.019558</v>
+        <v>-0.02076</v>
       </c>
     </row>
     <row r="107">
@@ -18933,7 +18933,11 @@
           <t>Increase in prepaids and deposits</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -20578,7 +20582,11 @@
           <t>(Increase)/decrease in prepaids and deposits</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -21479,7 +21487,11 @@
           <t>Decrease in prepaids and deposits</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -23452,7 +23464,11 @@
           <t>(Increase)/decrease in prepaids and deposits</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -23991,7 +24007,11 @@
           <t>(Increase)/decrease in prepaids and deposits</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -24304,7 +24324,11 @@
           <t>(Increase) decrease in prepaids and deposits</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E143" s="5" t="n">
         <v>0.099117</v>
       </c>
@@ -25935,7 +25959,11 @@
           <t>(Increase) decrease in prepaids and deposits 1,089</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BKM.xlsx
+++ b/output/pdf_financials_xlsx/BKM.xlsx
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.209308</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.173848</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.020436</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>-0.01461</v>
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.221907</v>
+        <v>-2.012599</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.22973</v>
+        <v>-2.055882</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.254085</v>
+        <v>-2.233649</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-2.105305</v>
@@ -2297,13 +2297,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.221907</v>
+        <v>-2.012599</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.22973</v>
+        <v>-2.055882</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.254085</v>
+        <v>-2.233649</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-2.07619</v>
@@ -8608,10 +8608,10 @@
         <v>0</v>
       </c>
       <c r="S124" s="3" t="n">
-        <v>0</v>
+        <v>-0.04662</v>
       </c>
       <c r="T124" s="3" t="n">
-        <v>0</v>
+        <v>-0.04662</v>
       </c>
     </row>
     <row r="125">
@@ -8672,10 +8672,10 @@
         <v>0</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>0</v>
+        <v>-0.04662</v>
       </c>
       <c r="T125" s="3" t="n">
-        <v>0</v>
+        <v>-0.04662</v>
       </c>
     </row>
     <row r="126">
@@ -10180,7 +10180,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -15503,7 +15507,11 @@
           <t>Reclamation deposits 123,600</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -17160,7 +17168,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -19381,7 +19393,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -42603,7 +42619,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E312" s="5" t="n">

--- a/output/pdf_financials_xlsx/BKM.xlsx
+++ b/output/pdf_financials_xlsx/BKM.xlsx
@@ -2282,7 +2282,7 @@
         <v>0.005609</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>0.005475</v>
+        <v>0.039536</v>
       </c>
       <c r="T28" s="1" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>-0.515888</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-0.624129</v>
+        <v>-0.590068</v>
       </c>
       <c r="T29" s="1" t="inlineStr">
         <is>
@@ -7070,10 +7070,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="3" t="n">
-        <v>0</v>
+        <v>0.039536</v>
       </c>
       <c r="T100" s="3" t="n">
-        <v>0</v>
+        <v>0.039536</v>
       </c>
     </row>
     <row r="101">
@@ -18442,7 +18442,11 @@
           <t>Depreciation-right-of-use assets</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -20275,7 +20279,11 @@
           <t>Depreciation-Right-of-use assets</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
